--- a/2022 data/excel_outputs/231_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/231_boothwise_data.xlsx
@@ -14,761 +14,1304 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="477">
   <si>
     <t>AC 231 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#0 ####0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ###### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ###### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ###### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ###### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>############## #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>############## #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### ########</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>####0##0###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;######ddh</t>
-  </si>
-  <si>
-    <t>##0##0##0 #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ########## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ########## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ##### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ##### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### ##### #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##### ######</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ###### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########### ########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 #######</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ####### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ####### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ############## ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######### #### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #########</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0#0##0###### #### ##0 6</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### ####### ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ############</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### #######</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ####### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0####0##0 ####### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########## #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ####### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### #0####0##0 ####### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 3</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 4</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 5</t>
-  </si>
-  <si>
-    <t>#0#0##0 ####### #### ##0 6</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ###### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ####### ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ## ####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #####</t>
-  </si>
-  <si>
-    <t>######### ###### #### ########</t>
-  </si>
-  <si>
-    <t>######### ###### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## #### ### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## #### ### 2</t>
-  </si>
-  <si>
-    <t>##### ###### ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ########## ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ###### ######## #### ### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ######## #### ### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
+    <t>A0 V0RAJAUNI</t>
+  </si>
+  <si>
+    <t>A0 V0 PARAUVAR</t>
+  </si>
+  <si>
+    <t>A0 V0 KH RAYAKHAD U</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 PACHARA</t>
+  </si>
+  <si>
+    <t>NAN</t>
+  </si>
+  <si>
+    <t>A0 V0 THURAT K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 THURAT K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAM GAPURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR K SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR K SAM0 4</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR U#TAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 JAITAPUR U#TAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 NAYAPURA JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 NAYAPURA JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BUDHAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 KH RAYA KALAM</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 KUDAI</t>
+  </si>
+  <si>
+    <t>A0 V0 HAM SALA</t>
+  </si>
+  <si>
+    <t>A0 V0 GADH U A</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS RAYA JAITAPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 ,TAK RAYA JAITAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 ,TAK RAYA JAITAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 MAVAIYA</t>
+  </si>
+  <si>
+    <t>A0 V0MAG RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 JAILAVARA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0AR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0AR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 LADAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGHAURA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGHAURA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SIGAUN K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SIGAUN K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAM/VA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 NARAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAMA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAMA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 PATHAR NAUAVAD</t>
+  </si>
+  <si>
+    <t>A0 V0 JAGATAPUR UPH G,DHAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 GHASALANI</t>
+  </si>
+  <si>
+    <t>A0 V0 RAVATAPURA KHALASA</t>
+  </si>
+  <si>
+    <t>A0 V0 GAMJ</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAVARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 DHAVARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 2BAJAUR</t>
+  </si>
+  <si>
+    <t>A0 V0 GHAMGHAURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BUDHAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 BUDHAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 I45HATA</t>
+  </si>
+  <si>
+    <t>A0 V0 PASANAVAD</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 SAGU NAYAMAPH K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 SAGU NAYAMAPH K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 NAGARADAMG K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 NAGARADAMG K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAGAR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 SALAIYAMAPH</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 7YAVAN K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 7YAVAN K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 G8 U D</t>
+  </si>
+  <si>
+    <t>A0 V0 RAJAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAMANAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGAUL</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 H RAJAN B7TI AJANAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 H RAJAN B7TI AJANAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 H RAJAN B7TI AJANAR K SAM0 3</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AJANAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AJANAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BADERA KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 BADAKHERA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 PURAVA JAITAPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 BACHE CHAR KALAM</t>
+  </si>
+  <si>
+    <t>A0 V0 BER</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MAGARAUL KALAM K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MAGARAUL KALAM K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MAGARAUL KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHE VA</t>
+  </si>
+  <si>
+    <t>A0 V0 KUTARA</t>
+  </si>
+  <si>
+    <t>A0 V0 MUDHAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 MUDHAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>K4YA A0 V0 MUDHAR</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 MUDHAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 MUDHAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 ,TAK RAYA PANAVADI</t>
+  </si>
+  <si>
+    <t>A0 V0 LAMAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BACHE CHAR KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 AKAUNI</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AKAUNA K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AKAUNA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 KAITHORA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KAITHAURA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 ARAGHATAMAU</t>
+  </si>
+  <si>
+    <t>A0 V0 MAJHAGAVAMKHAD U</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MAHUABAMDH</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHUABAMDH</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 MAHUABAMDH</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMUPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 PURAVAPANAVADI</t>
+  </si>
+  <si>
+    <t>A0 V0 BAMAU&gt;LAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 LEVA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGAU&gt;LAYA BUJUG</t>
+  </si>
+  <si>
+    <t>A0 V0 RAKHAVAHA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAIR RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGAVAHA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGAVAHA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BHADARAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 NANAVARA</t>
+  </si>
+  <si>
+    <t>A0 V0 RAGAU&gt;LAYA KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 NATARA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 NAUGAMV</t>
+  </si>
+  <si>
+    <t>A0 V0 PHADANA</t>
+  </si>
+  <si>
+    <t>A0 V0 NAKARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 NAKARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 NAKARA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAGAMRA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 JAKHA</t>
+  </si>
+  <si>
+    <t>A0 V0 SHERAGADH</t>
+  </si>
+  <si>
+    <t>A0 V0 TURAMUHAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 TURAMUHAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SALAIYA KHALASA</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 7YODH K SAM0 1</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 7YODH K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 RAYAPURA MAJARA 7YODH</t>
+  </si>
+  <si>
+    <t>A0 V0 GAUNAGADH U A</t>
+  </si>
+  <si>
+    <t>A0 V0 HAI VATAPURA KHAGAMRAN</t>
+  </si>
+  <si>
+    <t>A0 V0 MASUDAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 NEKAPURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 &gt;SALALAPURA</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 NAGARAGHAT</t>
+  </si>
+  <si>
+    <t>BALAK A0 V0 NAGARAGHAT</t>
+  </si>
+  <si>
+    <t>A0 V0 &gt;LADHAURAKHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 BUDARE O</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BUDARE O</t>
+  </si>
+  <si>
+    <t>A0 V0 LAULARA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AL PURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAIDAA</t>
+  </si>
+  <si>
+    <t>K0U0MA0 V0 BAIDAA K SAM0 1</t>
+  </si>
+  <si>
+    <t>K0U0MA0 V0 BAIDAA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 MARAGAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 GARABL</t>
+  </si>
+  <si>
+    <t>A0 V0 CHAMCHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 JAGAPURA BUJUG</t>
+  </si>
+  <si>
+    <t>A0 V0 /R KHAD U</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 KOTARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 KOTARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BIHAT</t>
+  </si>
+  <si>
+    <t>A0 V0 LOHARAGAMV</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 NAIPURA K SAM0 1</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 NAIPURA K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MADAVAR</t>
+  </si>
+  <si>
+    <t>A0 V0 KOH NAYAM K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 KO,HANAYAM K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 DHARAVAR</t>
+  </si>
+  <si>
+    <t>A0 V0 RACHARA</t>
+  </si>
+  <si>
+    <t>A0 V0 ,TAK RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 &gt;LALAVAM</t>
+  </si>
+  <si>
+    <t>A0 V0 TAPARAN</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 KASHIPUR</t>
+  </si>
+  <si>
+    <t>A0 V0 MADHAUGAMJ</t>
+  </si>
+  <si>
+    <t>A0 V0 KARAPAHACDAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 UMARAI</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 TEIYA K SAM0 1</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 TEIYA K SAM0 2</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 CHAMARA</t>
+  </si>
+  <si>
+    <t>A0 V0 SAURA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SAURA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 RAVATAPUR KALAM</t>
+  </si>
+  <si>
+    <t>A0 V0 MANAKAD</t>
+  </si>
+  <si>
+    <t>A0 V0 KARAHARAKHAD U KHAIRO</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CHAUKA K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CHAUKA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGARAUNI</t>
+  </si>
+  <si>
+    <t>A0 V0 GADAU</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 TEL PAHADI</t>
+  </si>
+  <si>
+    <t>A0 V0 GHUTAI K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 GHUTAI K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0A&gt;M&gt;LAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 PAPAR</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 KANAURA</t>
+  </si>
+  <si>
+    <t>A0 V0GADAURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 /R KALAM K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 /R KALAM K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 KANAKUVAM</t>
+  </si>
+  <si>
+    <t>A0 V0 KANAKAMU VA</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 MAHOBAKAMTH (PUVAE PAFV)</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 MAHOBAKAMTH (PAFCHAMI PAFV)</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAIROKALAM</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGHAUR KU&gt;MAN</t>
+  </si>
+  <si>
+    <t>A0 V0 BHURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DHAVAR</t>
+  </si>
+  <si>
+    <t>A0 V0 SATAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BAS RAYA PANAVADI</t>
+  </si>
+  <si>
+    <t>A0 V0 BAHADARU PUR KALAM</t>
+  </si>
+  <si>
+    <t>A0 V0 ,DADAVARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 ,DADAVARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DE VAGANAPURA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 AL PURA</t>
+  </si>
+  <si>
+    <t>A0 V0 HE VATAPURA HGHANAN</t>
+  </si>
+  <si>
+    <t>A0 V0 SARAGAPURA</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 1</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 2</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 3</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 4</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 5</t>
+  </si>
+  <si>
+    <t>RA0BA0I0KA0 PANAVADI K SAM0 6</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 1</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 2</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 3</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 4</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 5</t>
+  </si>
+  <si>
+    <t>NE0I0KA0PANAVADI K SAM0 6</t>
+  </si>
+  <si>
+    <t>A0 V0 RAHU NAYAPURA PANAVADI</t>
+  </si>
+  <si>
+    <t>A0 V0 &gt;SAM RAYA</t>
+  </si>
+  <si>
+    <t>A0 V0 UIDAN</t>
+  </si>
+  <si>
+    <t>A0 V0 LODHIPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 2BAJARAR</t>
+  </si>
+  <si>
+    <t>A0 V0 JKAIHAUVA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 JKAIHAUVA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 JKAIHAUVA K SAM0 3</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BUDAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 GUGAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 KHEDA NANAKAR</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 MAHUVAITAURA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 MAHUVAITAURA</t>
+  </si>
+  <si>
+    <t>A0 V0 CHATESAR</t>
+  </si>
+  <si>
+    <t>A0 V0 KO NAYAM</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 PAHACDAYA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 ITAURABUJUG</t>
+  </si>
+  <si>
+    <t>A0 V0 KUNATA</t>
+  </si>
+  <si>
+    <t>A0 V0 ,TAMGARA</t>
+  </si>
+  <si>
+    <t>A0 V0 PARAPAMTAR</t>
+  </si>
+  <si>
+    <t>A0 V0 RAVAI</t>
+  </si>
+  <si>
+    <t>A0 V0 TOLAPAMTAR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DAL U ARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DAL U ARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 AMANAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 BHUJAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 SAMTHAR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 DADAR</t>
+  </si>
+  <si>
+    <t>A0 V0 GHATE RA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 2BAHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 SATAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 SATAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 CHURAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 CHURAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BHARAVARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BHARAVARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BHARAVARA K SAM0 3</t>
+  </si>
+  <si>
+    <t>A0 V0 BHARAVARA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 PATHAR KAD M</t>
+  </si>
+  <si>
+    <t>A0 V0 CHA/VA</t>
+  </si>
+  <si>
+    <t>A0 V0 RACHA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 VAJAYAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 VAJAYAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 PANARA</t>
+  </si>
+  <si>
+    <t>AVADHAT U ANAMD PU0MA0 V0 A8DAVARA K SAM0 1</t>
+  </si>
+  <si>
+    <t>AVADHAT U ANAMD PU0MA0 V0 A8DAVARA K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BAGAUL</t>
+  </si>
+  <si>
+    <t>A0 V0 BUDH</t>
+  </si>
+  <si>
+    <t>A0 V0 BAURA</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 SUKGAMRA K SAM0 1</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 SUKGAMRA K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 SUKGAMRA</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 SUKGAMRA</t>
+  </si>
+  <si>
+    <t>A0 V0 GADH SUKGAMRA</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 KULAPAHAD KALA SAM0 1</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 KULAPAHAD KALA SAM0 2</t>
+  </si>
+  <si>
+    <t>K0PU0MA0 V0 KULAPAHAD KALA SAM0 3</t>
+  </si>
+  <si>
+    <t>SAMT2BANOVA A0 V0 KULAPAHAD K SAM0 1</t>
+  </si>
+  <si>
+    <t>SAMT2BANOVA A0 V0 KULAPAHAD K SAM0 2</t>
+  </si>
+  <si>
+    <t>MADAL 7KUL KULAPAHAD K SAM0 1</t>
+  </si>
+  <si>
+    <t>MADAL 7KUL KULAPAHAD K SAM0 2</t>
+  </si>
+  <si>
+    <t>MADAL 7KUL KULAPAHAD K SAM0 3</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 1</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 2</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 3</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 4</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 5</t>
+  </si>
+  <si>
+    <t>J0I0KA0 KULAPAHAD K SAM0 6</t>
+  </si>
+  <si>
+    <t>A0 V0 RE IVE 7TE SHAN KULAPAHAD</t>
+  </si>
+  <si>
+    <t>A0 V0 SAILAKHALASA</t>
+  </si>
+  <si>
+    <t>A0 V0 KAMALAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 ATARAPATHA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 LADAPUR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 LADAPUR K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 MAUHAR</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 MAUHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 BAGHAUR KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 DARAYAV &gt;SAMH KA KHUDA</t>
+  </si>
+  <si>
+    <t>A0 V0 &gt;SARAMAUR</t>
+  </si>
+  <si>
+    <t>A0 V0BHATE VARAKHUD K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0BHATE VARAKHUD K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 RAVATAPURA KHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0 KHAUN RAYA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 THATHE VARA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 GORAKHA</t>
+  </si>
+  <si>
+    <t>A0 V0 CHE D MAU</t>
+  </si>
+  <si>
+    <t>A0 V0 RAMAPURA KAD M</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 LUHAR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AKATHAUHAM K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 AKATHAUHAM K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 AKATHAUHAM</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 Gढ़ U A</t>
+  </si>
+  <si>
+    <t>JKASAN SEVA KE45 Gढ़ U A</t>
+  </si>
+  <si>
+    <t>A0 V0 Gढ़ U A</t>
+  </si>
+  <si>
+    <t>A0 V0 K BHATE VARAKALAM SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 BHATE VARAKALAM K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 GAURAHAR K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 GAURAHAR K SAM0 2</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 GAURAHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 KARAHARAKHAD U</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KARAHARAKHURD</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 BAQRE THA</t>
+  </si>
+  <si>
+    <t>A0 V0 ANAGHAURA K SAM0 1</t>
+  </si>
+  <si>
+    <t>A0 V0 ANAGHAURA K SAM0 2</t>
+  </si>
+  <si>
+    <t>VANYAN4D PU0MA0 V0 JARAUL K SAM0 1</t>
+  </si>
+  <si>
+    <t>VANYAN4D PU0MA0 V0 JARAUL K SAM0 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BAILAYAM</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CH4DAUL K SAM0 1</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CH4DAUL K SAM0 2</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 KU.DAR</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 RAVAI</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 RAVAI</t>
+  </si>
+  <si>
+    <t>N0 A0 V0 RAVAI</t>
+  </si>
+  <si>
+    <t>A0 V0 SAMTOSHAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 SABUA</t>
+  </si>
+  <si>
+    <t>A0 V0 GHAT U VAI</t>
+  </si>
+  <si>
+    <t>A0 V0 KUSARAMA</t>
+  </si>
+  <si>
+    <t>A0 V0BAGHAUR KHAD U</t>
+  </si>
+  <si>
+    <t>NAVIN A0 V0SUDAMAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 CHANIKHAD U</t>
+  </si>
+  <si>
+    <t>A0 V0KANERA</t>
+  </si>
+  <si>
+    <t>A0 V0NAUSARA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0JATAURA</t>
+  </si>
+  <si>
+    <t>A0 V0NATARA</t>
+  </si>
+  <si>
+    <t>A0 V0PAMCHAMAPURA</t>
+  </si>
+  <si>
+    <t>A0 V0 KADRATAPURA</t>
+  </si>
+  <si>
+    <t>K0 A0 V0 BAGHAUR KALA</t>
+  </si>
+  <si>
+    <t>N0 A0 V0BAGHAUR KALA</t>
+  </si>
+  <si>
+    <t>A0 V0 &gt;SHAVAHAR</t>
+  </si>
+  <si>
+    <t>A0 V0 BAMARARA</t>
+  </si>
+  <si>
+    <t>K4YA JU0HA07KUL BAMARARA</t>
   </si>
   <si>
     <t>puu0maa0vi0 krhraakhurd</t>
   </si>
   <si>
-    <t>■■0■■0■■0 ■Q■■■■ ■■■■■■■■ ■■■■ ■■■ 1</t>
-  </si>
-  <si>
-    <t>■■0■■0■■0 ■Q■■■■ ■■■■■■■■ ■■■■ ■■■ 2</t>
-  </si>
-  <si>
-    <t>########## ##0##0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>########## ##0##0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ####### ########</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### kkss sN 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### kkss sN 2</t>
-  </si>
-  <si>
-    <t>######## #### ######## #### ###-1</t>
-  </si>
-  <si>
-    <t>######## #### ######## #### ###-2</t>
-  </si>
-  <si>
-    <t>######## #### ######## ####### 3</t>
-  </si>
-  <si>
-    <t>####0##0############</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>##0##0##0#####</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>######### ######## ########</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##########</t>
-  </si>
-  <si>
-    <t>#0####0##0########## kkss sN 1</t>
-  </si>
-  <si>
-    <t>#0####0##0########## kkss sN 2</t>
-  </si>
-  <si>
-    <t>########### ###### ######## #### ### 1</t>
-  </si>
-  <si>
-    <t>########### ###### ######## #### ### 2</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ########### #### ##0-1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ########### kkss sN0-2</t>
-  </si>
-  <si>
-    <t>######### ########## ########</t>
+    <t>N0 A0 V0 IJHAMAJHALAYADAMG KAKSH SAM0-2</t>
+  </si>
+  <si>
+    <t>A0 V0 MAHARAJAPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BRRIJAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 SUHAJANA</t>
+  </si>
+  <si>
+    <t>PU0MA0 V0 ROSHANAPURA</t>
+  </si>
+  <si>
+    <t>RA0BA0IM0KA0 CHARAKHAR KAKSH-1</t>
+  </si>
+  <si>
+    <t>RA0BA0IM0KA0CHARAKHAR K -SAM-2</t>
+  </si>
+  <si>
+    <t>RA0BA0IM0KA0CHARAKHAR K -SAM-3</t>
+  </si>
+  <si>
+    <t>RA0BA0IM0KA0CHARAKHAR K -SAM-4</t>
+  </si>
+  <si>
+    <t>A0 V0 JAYE45NAGAR CHARAKHAR K .1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAYENDRANAGAR CHARAKHARI (ATIRIKT KAKSH )</t>
+  </si>
+  <si>
+    <t>A0 V0 JAYE45NAGAR CHARAKHAR K .2</t>
+  </si>
+  <si>
+    <t>U0 A0 V0TALAKOTHAPH, CHINTEPURA CHARAKHAR KAKSH SAM0-1</t>
+  </si>
+  <si>
+    <t>U0 A0 V0TALAKOTHAPH, CHINTEPURA CHARAKHAR K . 2</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAIR|GAMJ CHARAKHARI K .1</t>
+  </si>
+  <si>
+    <t>A0 V0 BHAIRAAGAMJ CHARAKHAR K -2</t>
+  </si>
+  <si>
+    <t>K0 A0 V0SADAR BAJAR CHARAKHAR K -1</t>
+  </si>
+  <si>
+    <t>K0 A0 V0SADAR BAJAR CHARAKHAR K SAM-2</t>
+  </si>
+  <si>
+    <t>RA0GAMGA&gt;SAMH IM0KA0 CHARAKHAR K -1</t>
+  </si>
+  <si>
+    <t>RA0GAMGA&gt;SAMH IM0KA0 CHARAKHAR K -2</t>
+  </si>
+  <si>
+    <t>RA0GAMGA&gt;SAMH IM0KA0 CHARAKHAR K -3</t>
+  </si>
+  <si>
+    <t>A0 V0JAJHU ARAGAMJ KH,DAYAPARU A CHARAKHAR</t>
+  </si>
+  <si>
+    <t>K0PRA0VI0 SUHARAYAMV CHARAKHARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMANAGAR, CHARAKHARI</t>
+  </si>
+  <si>
+    <t>U0PRA0VI0 JAYANTIDEVI AMARAGAMJ, CHARAKHARI KAKSH SAM0-1</t>
+  </si>
+  <si>
+    <t>U0PRA0VI0 JAYANTIDEVI AMARAGAMJ, CHARAKHARI KAKSH SAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KURAURADAMG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHATEHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAISARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAGARAUN</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BAGARAUN</t>
+  </si>
+  <si>
+    <t>NAVIN PRA0VI0 ASTHAUN</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 ASTHAUN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAMHAURIBELADARAN</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SUPA KAKSH-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SUPA KAKSH-2</t>
   </si>
   <si>
     <t>praa0vi0 bRjpur</t>
   </si>
   <si>
-    <t>##0##0##0 ######## ########</t>
-  </si>
-  <si>
-    <t>##0##0##0##0 ###### kkss-1</t>
-  </si>
-  <si>
-    <t>##0##0##0##0###### ####.##.2</t>
-  </si>
-  <si>
-    <t>##0##0##0##0###### ####.##.3</t>
-  </si>
-  <si>
-    <t>##0##0##0##0###### ####.##.4</t>
-  </si>
-  <si>
-    <t>####0##0 #ye######## ###### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 #ye######## ###### ######## ####</t>
-  </si>
-  <si>
-    <t>######### ####### ######## ###### #### ### 1</t>
-  </si>
-  <si>
-    <t>######### ####### ######## ###### #### ### 2</t>
-  </si>
-  <si>
-    <t>######## ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## crkhaarii ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### ####.2</t>
-  </si>
-  <si>
-    <t>#0####0##0### ##### ###### ####.1</t>
-  </si>
-  <si>
-    <t>#0####0##0### ##### ###### #### ##.2</t>
-  </si>
-  <si>
-    <t>##0######## ##0##0 ###### ####.1</t>
-  </si>
-  <si>
-    <t>##0######## ##0##0 ###### ####.2</t>
-  </si>
-  <si>
-    <t>##0######## ##0##0 ###### ####.3</t>
-  </si>
-  <si>
-    <t>######### ###### ######## ######</t>
+    <t>KANYA PU0MA0VI0 SUPA KAKSH-2</t>
+  </si>
+  <si>
+    <t>KANYA PRA0VI0 SUPA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALAT</t>
+  </si>
+  <si>
+    <t>U0PRA0VI0 SALAT</t>
+  </si>
+  <si>
+    <t>KANYA PRA0VI0 SVASAMAPH</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>NAVIN PU0MA0VI0 TOLASOYAM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
   </si>
   <si>
     <t>k0praa0vi0 suhryaaNv crkhaarii</t>
   </si>
   <si>
+    <t>k0praa0vi0 suhryaaNv crkhaarii ROOM NO. 408</t>
+  </si>
+  <si>
     <t>u0praa0vi0 jyntiidevii amrgNj, crkhaarii kkss sN0-1</t>
   </si>
   <si>
@@ -799,7 +1342,7 @@
     <t>puu0maa0vi0 asthaun</t>
   </si>
   <si>
-    <t>######### ############### ########</t>
+    <t>puu0maa0vi0 asthaun ROOM NO. 419</t>
   </si>
   <si>
     <t>puu0maa0vi0 suupaa kkss-1</t>
@@ -811,10 +1354,10 @@
     <t>puu0maa0vi0 suupaa kkss-3</t>
   </si>
   <si>
-    <t>knyaa puu0maa0vi0 suupaa ######## kkss-1</t>
-  </si>
-  <si>
-    <t>knyaa puu0maa0vi0 suupaa ######## kkss-2</t>
+    <t>puu0maa0vi0 suupaa kkss-3 ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>puu0maa0vi0 suupaa kkss-3 ROOM ROOM NO. 424</t>
   </si>
   <si>
     <t>knyaa puu0maa0vi0 suupaa kmpojitt kkss sN0-3</t>
@@ -826,7 +1369,7 @@
     <t>u0praa0vi0 saaltt</t>
   </si>
   <si>
-    <t>praa0vi0 svaasaamaaph ########-1</t>
+    <t>u0praa0vi0 saaltt ROOM NO. 428</t>
   </si>
   <si>
     <t>praa0vi0svaasaamaaph kmpojitt -2</t>
@@ -835,7 +1378,10 @@
     <t>nviin puu0maa0vi0 ttolaasoym</t>
   </si>
   <si>
-    <t>######### ##### ########</t>
+    <t>nviin puu0maa0vi0 ttolaasoym ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>nviin puu0maa0vi0 ttolaasoym ROOM ROOM NO. 432</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -905,8 +1451,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -922,7 +1476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -930,12 +1484,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1234,79 +1806,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>457</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="F2" t="s">
-        <v>277</v>
+        <v>459</v>
       </c>
       <c r="G2" t="s">
-        <v>278</v>
+        <v>460</v>
       </c>
       <c r="H2" t="s">
-        <v>279</v>
+        <v>461</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>462</v>
       </c>
       <c r="J2" t="s">
-        <v>281</v>
+        <v>463</v>
       </c>
       <c r="K2" t="s">
-        <v>282</v>
+        <v>464</v>
       </c>
       <c r="L2" t="s">
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="M2" t="s">
-        <v>284</v>
+        <v>466</v>
       </c>
       <c r="N2" t="s">
-        <v>285</v>
+        <v>467</v>
       </c>
       <c r="O2" t="s">
-        <v>286</v>
+        <v>468</v>
       </c>
       <c r="P2" t="s">
-        <v>287</v>
+        <v>469</v>
       </c>
       <c r="Q2" t="s">
-        <v>288</v>
+        <v>470</v>
       </c>
       <c r="R2" t="s">
-        <v>289</v>
+        <v>471</v>
       </c>
       <c r="S2" t="s">
-        <v>290</v>
+        <v>472</v>
       </c>
       <c r="T2" t="s">
-        <v>291</v>
+        <v>473</v>
       </c>
       <c r="U2" t="s">
-        <v>292</v>
+        <v>474</v>
       </c>
       <c r="V2" t="s">
-        <v>293</v>
+        <v>475</v>
       </c>
       <c r="W2" t="s">
-        <v>294</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1314,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>1158</v>
@@ -1385,7 +2023,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>636</v>
@@ -1456,7 +2094,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>113</v>
@@ -1527,7 +2165,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1186</v>
@@ -1598,7 +2236,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1169</v>
@@ -1669,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1025</v>
@@ -1740,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>697</v>
@@ -1811,7 +2449,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>360</v>
@@ -1882,7 +2520,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>739</v>
@@ -1953,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>864</v>
@@ -2024,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>867</v>
@@ -2095,7 +2733,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>884</v>
@@ -2166,7 +2804,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>994</v>
@@ -2237,7 +2875,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>962</v>
@@ -2308,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1067</v>
@@ -2379,7 +3017,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>925</v>
@@ -2450,7 +3088,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>983</v>
@@ -2521,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>1019</v>
@@ -2592,7 +3230,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>965</v>
@@ -2663,7 +3301,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>717</v>
@@ -2734,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>776</v>
@@ -2805,7 +3443,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>881</v>
@@ -2876,7 +3514,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>823</v>
@@ -2947,7 +3585,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>922</v>
@@ -3018,7 +3656,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1024</v>
@@ -3089,7 +3727,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>641</v>
@@ -3160,7 +3798,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>624</v>
@@ -3231,7 +3869,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>863</v>
@@ -3302,7 +3940,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>431</v>
@@ -3373,7 +4011,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>843</v>
@@ -3444,7 +4082,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>366</v>
@@ -3515,7 +4153,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>787</v>
@@ -3586,7 +4224,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>800</v>
@@ -3657,7 +4295,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>590</v>
@@ -3728,7 +4366,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>701</v>
@@ -3799,7 +4437,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>847</v>
@@ -3870,7 +4508,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>716</v>
@@ -3941,7 +4579,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>1078</v>
@@ -4012,7 +4650,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>1000</v>
@@ -4083,7 +4721,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>1060</v>
@@ -4154,7 +4792,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>1049</v>
@@ -4225,7 +4863,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>1163</v>
@@ -4296,7 +4934,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>832</v>
@@ -4367,7 +5005,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>750</v>
@@ -4438,7 +5076,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>641</v>
@@ -4509,7 +5147,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>1079</v>
@@ -4580,7 +5218,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>720</v>
@@ -4651,7 +5289,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>639</v>
@@ -4722,7 +5360,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>669</v>
@@ -4793,7 +5431,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>458</v>
@@ -4864,7 +5502,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>418</v>
@@ -4935,7 +5573,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>228</v>
@@ -5006,7 +5644,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>604</v>
@@ -5077,7 +5715,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>926</v>
@@ -5148,7 +5786,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>1129</v>
@@ -5219,7 +5857,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>1102</v>
@@ -5290,7 +5928,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>779</v>
@@ -5361,7 +5999,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>737</v>
@@ -5432,7 +6070,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>1032</v>
@@ -5503,7 +6141,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1044</v>
@@ -5574,7 +6212,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>1101</v>
@@ -5645,7 +6283,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>512</v>
@@ -5716,7 +6354,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>756</v>
@@ -5787,7 +6425,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>976</v>
@@ -5858,7 +6496,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>802</v>
@@ -5929,7 +6567,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>947</v>
@@ -6000,7 +6638,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>1157</v>
@@ -6071,7 +6709,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>735</v>
@@ -6142,7 +6780,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>730</v>
@@ -6213,7 +6851,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>991</v>
@@ -6284,7 +6922,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>570</v>
@@ -6355,7 +6993,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>496</v>
@@ -6426,7 +7064,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>482</v>
@@ -6497,7 +7135,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>454</v>
@@ -6568,7 +7206,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>235</v>
@@ -6639,7 +7277,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>720</v>
@@ -6710,7 +7348,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>1147</v>
@@ -6781,7 +7419,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>1009</v>
@@ -6852,7 +7490,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>1065</v>
@@ -6923,7 +7561,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1205</v>
@@ -6994,7 +7632,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1211</v>
@@ -7065,7 +7703,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>879</v>
@@ -7136,7 +7774,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>593</v>
@@ -7207,7 +7845,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>670</v>
@@ -7278,7 +7916,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>590</v>
@@ -7349,7 +7987,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>519</v>
@@ -7420,7 +8058,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>930</v>
@@ -7491,7 +8129,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>1106</v>
@@ -7562,7 +8200,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>351</v>
@@ -7633,7 +8271,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>853</v>
@@ -7704,7 +8342,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>334</v>
@@ -7775,7 +8413,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>840</v>
@@ -7846,7 +8484,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>857</v>
@@ -7917,7 +8555,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>736</v>
@@ -7988,7 +8626,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>658</v>
@@ -8059,7 +8697,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>677</v>
@@ -8130,7 +8768,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>712</v>
@@ -8201,7 +8839,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>657</v>
@@ -8272,7 +8910,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>756</v>
@@ -8343,7 +8981,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>435</v>
@@ -8414,7 +9052,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>651</v>
@@ -8485,7 +9123,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>688</v>
@@ -8556,7 +9194,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>1032</v>
@@ -8627,7 +9265,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>724</v>
@@ -8698,7 +9336,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>983</v>
@@ -8769,7 +9407,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>828</v>
@@ -8840,7 +9478,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>788</v>
@@ -8911,7 +9549,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>882</v>
@@ -8982,7 +9620,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>749</v>
@@ -9053,7 +9691,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>574</v>
@@ -9124,7 +9762,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>1042</v>
@@ -9195,7 +9833,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>1124</v>
@@ -9266,7 +9904,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>1093</v>
@@ -9337,7 +9975,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>850</v>
@@ -9408,7 +10046,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>870</v>
@@ -9479,7 +10117,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>380</v>
@@ -9550,7 +10188,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>751</v>
@@ -9621,7 +10259,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>999</v>
@@ -9692,7 +10330,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>757</v>
@@ -9763,7 +10401,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>509</v>
@@ -9834,7 +10472,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>710</v>
@@ -9905,7 +10543,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>641</v>
@@ -9976,7 +10614,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>229</v>
@@ -10047,7 +10685,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>588</v>
@@ -10118,7 +10756,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>705</v>
@@ -10189,7 +10827,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>610</v>
@@ -10260,7 +10898,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>646</v>
@@ -10331,7 +10969,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>526</v>
@@ -10402,7 +11040,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>605</v>
@@ -10473,7 +11111,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>817</v>
@@ -10544,7 +11182,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>855</v>
@@ -10615,7 +11253,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>1177</v>
@@ -10686,7 +11324,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>39</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>419</v>
@@ -10757,7 +11395,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>818</v>
@@ -10828,7 +11466,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>787</v>
@@ -10899,7 +11537,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>728</v>
@@ -10970,7 +11608,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>954</v>
@@ -11041,7 +11679,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>820</v>
@@ -11112,7 +11750,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>728</v>
@@ -11183,7 +11821,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>850</v>
@@ -11254,7 +11892,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>895</v>
@@ -11325,7 +11963,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>948</v>
@@ -11396,7 +12034,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>995</v>
@@ -11467,7 +12105,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>118</v>
@@ -11538,7 +12176,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>524</v>
@@ -11609,7 +12247,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>778</v>
@@ -11680,7 +12318,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>705</v>
@@ -11751,7 +12389,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>65</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>686</v>
@@ -11822,7 +12460,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>871</v>
@@ -11893,7 +12531,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>847</v>
@@ -11964,7 +12602,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>861</v>
@@ -12035,7 +12673,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>949</v>
@@ -12106,7 +12744,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>902</v>
@@ -12177,7 +12815,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1016</v>
@@ -12248,7 +12886,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>1208</v>
@@ -12319,7 +12957,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>550</v>
@@ -12390,7 +13028,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>813</v>
@@ -12461,7 +13099,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>734</v>
@@ -12532,7 +13170,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>851</v>
@@ -12603,7 +13241,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>892</v>
@@ -12674,7 +13312,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>345</v>
@@ -12745,7 +13383,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>523</v>
@@ -12816,7 +13454,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>476</v>
@@ -12887,7 +13525,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>264</v>
@@ -12958,7 +13596,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>411</v>
@@ -13029,7 +13667,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>726</v>
@@ -13100,7 +13738,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>807</v>
@@ -13171,7 +13809,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>663</v>
@@ -13242,7 +13880,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>1009</v>
@@ -13313,7 +13951,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>791</v>
@@ -13384,7 +14022,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>870</v>
@@ -13455,7 +14093,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>54</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>890</v>
@@ -13526,7 +14164,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>822</v>
@@ -13597,7 +14235,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>821</v>
@@ -13668,7 +14306,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>907</v>
@@ -13739,7 +14377,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>26</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>573</v>
@@ -13810,7 +14448,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>104</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>1140</v>
@@ -13881,7 +14519,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>623</v>
@@ -13952,7 +14590,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>576</v>
@@ -14023,7 +14661,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1168</v>
@@ -14094,7 +14732,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>455</v>
@@ -14165,7 +14803,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>524</v>
@@ -14236,7 +14874,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>1143</v>
@@ -14307,7 +14945,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>966</v>
@@ -14378,7 +15016,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>1026</v>
@@ -14449,7 +15087,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>638</v>
@@ -14520,7 +15158,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>914</v>
@@ -14591,7 +15229,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>901</v>
@@ -14662,7 +15300,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>895</v>
@@ -14733,7 +15371,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>597</v>
@@ -14804,7 +15442,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>450</v>
@@ -14875,7 +15513,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>234</v>
@@ -14946,7 +15584,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>760</v>
@@ -15017,7 +15655,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>810</v>
@@ -15088,7 +15726,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>881</v>
@@ -15159,7 +15797,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>789</v>
@@ -15230,7 +15868,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>739</v>
@@ -15301,7 +15939,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>724</v>
@@ -15372,7 +16010,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>7</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>1108</v>
@@ -15443,7 +16081,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>8</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>811</v>
@@ -15514,7 +16152,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>314</v>
@@ -15585,7 +16223,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>1056</v>
@@ -15656,7 +16294,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>339</v>
@@ -15727,7 +16365,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>63</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>501</v>
@@ -15798,7 +16436,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>507</v>
@@ -15869,7 +16507,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>126</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>1012</v>
@@ -15940,7 +16578,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>1012</v>
@@ -16011,7 +16649,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>1008</v>
@@ -16082,7 +16720,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>129</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>1011</v>
@@ -16153,7 +16791,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>869</v>
@@ -16224,7 +16862,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>910</v>
@@ -16295,7 +16933,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>4</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>789</v>
@@ -16366,7 +17004,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>687</v>
@@ -16437,7 +17075,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>618</v>
@@ -16508,7 +17146,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>989</v>
@@ -16579,7 +17217,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>375</v>
@@ -16650,7 +17288,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>547</v>
@@ -16721,7 +17359,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>132</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>1086</v>
@@ -16792,7 +17430,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>1183</v>
@@ -16863,7 +17501,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>833</v>
@@ -16934,7 +17572,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>1164</v>
@@ -17005,7 +17643,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>676</v>
@@ -17076,7 +17714,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>291</v>
@@ -17147,7 +17785,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>39</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>249</v>
@@ -17218,7 +17856,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>768</v>
@@ -17289,7 +17927,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>786</v>
@@ -17360,7 +17998,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>826</v>
@@ -17431,7 +18069,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>140</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>1115</v>
@@ -17502,7 +18140,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>141</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>791</v>
@@ -17573,7 +18211,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>962</v>
@@ -17644,7 +18282,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>143</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>714</v>
@@ -17715,7 +18353,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>840</v>
@@ -17786,7 +18424,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>729</v>
@@ -17857,7 +18495,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>944</v>
@@ -17928,7 +18566,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>147</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>966</v>
@@ -17999,7 +18637,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>1070</v>
@@ -18070,7 +18708,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>149</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>1177</v>
@@ -18141,7 +18779,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>39</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>688</v>
@@ -18212,7 +18850,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>251</v>
@@ -18283,7 +18921,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>4</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>676</v>
@@ -18354,7 +18992,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>104</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>1033</v>
@@ -18425,7 +19063,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>116</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>1117</v>
@@ -18496,7 +19134,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>1038</v>
@@ -18567,7 +19205,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>973</v>
@@ -18638,7 +19276,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>47</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>590</v>
@@ -18709,7 +19347,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>1051</v>
@@ -18780,7 +19418,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>265</v>
@@ -18851,7 +19489,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>152</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>882</v>
@@ -18922,7 +19560,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>153</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>966</v>
@@ -18993,7 +19631,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>30</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>613</v>
@@ -19064,7 +19702,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>104</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>562</v>
@@ -19135,7 +19773,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>725</v>
@@ -19206,7 +19844,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>734</v>
@@ -19277,7 +19915,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>903</v>
@@ -19348,7 +19986,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>823</v>
@@ -19419,7 +20057,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>39</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>1169</v>
@@ -19490,7 +20128,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>817</v>
@@ -19561,7 +20199,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>157</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>675</v>
@@ -19632,7 +20270,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="C261">
         <v>682</v>
@@ -19703,7 +20341,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>61</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>744</v>
@@ -19774,7 +20412,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>62</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>747</v>
@@ -19845,7 +20483,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>10</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>1029</v>
@@ -19916,7 +20554,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>11</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>958</v>
@@ -19987,7 +20625,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>4</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>665</v>
@@ -20058,7 +20696,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>39</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>874</v>
@@ -20129,7 +20767,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>30</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>407</v>
@@ -20200,7 +20838,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>648</v>
@@ -20271,7 +20909,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>586</v>
@@ -20342,7 +20980,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>30</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>693</v>
@@ -20413,7 +21051,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>658</v>
@@ -20484,7 +21122,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>36</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>580</v>
@@ -20555,7 +21193,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>753</v>
@@ -20626,7 +21264,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>160</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>814</v>
@@ -20697,7 +21335,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>161</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>735</v>
@@ -20768,7 +21406,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>998</v>
@@ -20839,7 +21477,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>100</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>695</v>
@@ -20910,7 +21548,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>794</v>
@@ -20981,7 +21619,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>11</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>781</v>
@@ -21052,7 +21690,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>12</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>945</v>
@@ -21123,7 +21761,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>26</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>503</v>
@@ -21194,7 +21832,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>407</v>
@@ -21265,7 +21903,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>614</v>
@@ -21336,7 +21974,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>829</v>
@@ -21407,7 +22045,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>739</v>
@@ -21478,7 +22116,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>964</v>
@@ -21549,7 +22187,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="C288">
         <v>581</v>
@@ -21620,7 +22258,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
       <c r="C289">
         <v>594</v>
@@ -21691,7 +22329,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>165</v>
+        <v>311</v>
       </c>
       <c r="C290">
         <v>899</v>
@@ -21762,7 +22400,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>166</v>
+        <v>312</v>
       </c>
       <c r="C291">
         <v>552</v>
@@ -21833,7 +22471,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>63</v>
+        <v>313</v>
       </c>
       <c r="C292">
         <v>620</v>
@@ -21904,7 +22542,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>31</v>
+        <v>314</v>
       </c>
       <c r="C293">
         <v>155</v>
@@ -21975,7 +22613,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>31</v>
+        <v>315</v>
       </c>
       <c r="C294">
         <v>1169</v>
@@ -22046,7 +22684,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>133</v>
+        <v>316</v>
       </c>
       <c r="C295">
         <v>897</v>
@@ -22117,7 +22755,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="C296">
         <v>825</v>
@@ -22188,7 +22826,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>167</v>
+        <v>318</v>
       </c>
       <c r="C297">
         <v>674</v>
@@ -22259,7 +22897,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>168</v>
+        <v>319</v>
       </c>
       <c r="C298">
         <v>674</v>
@@ -22330,7 +22968,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>169</v>
+        <v>320</v>
       </c>
       <c r="C299">
         <v>683</v>
@@ -22401,7 +23039,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>170</v>
+        <v>321</v>
       </c>
       <c r="C300">
         <v>660</v>
@@ -22472,7 +23110,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>171</v>
+        <v>322</v>
       </c>
       <c r="C301">
         <v>1148</v>
@@ -22543,7 +23181,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>172</v>
+        <v>323</v>
       </c>
       <c r="C302">
         <v>813</v>
@@ -22614,7 +23252,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>173</v>
+        <v>324</v>
       </c>
       <c r="C303">
         <v>961</v>
@@ -22685,7 +23323,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>174</v>
+        <v>325</v>
       </c>
       <c r="C304">
         <v>914</v>
@@ -22756,7 +23394,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>175</v>
+        <v>326</v>
       </c>
       <c r="C305">
         <v>1146</v>
@@ -22827,7 +23465,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>176</v>
+        <v>327</v>
       </c>
       <c r="C306">
         <v>1004</v>
@@ -22898,7 +23536,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>177</v>
+        <v>328</v>
       </c>
       <c r="C307">
         <v>664</v>
@@ -22969,7 +23607,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>178</v>
+        <v>329</v>
       </c>
       <c r="C308">
         <v>1157</v>
@@ -23040,7 +23678,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="C309">
         <v>1093</v>
@@ -23111,7 +23749,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>180</v>
+        <v>331</v>
       </c>
       <c r="C310">
         <v>940</v>
@@ -23182,7 +23820,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>181</v>
+        <v>332</v>
       </c>
       <c r="C311">
         <v>1037</v>
@@ -23253,7 +23891,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="C312">
         <v>964</v>
@@ -23324,7 +23962,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>183</v>
+        <v>334</v>
       </c>
       <c r="C313">
         <v>1031</v>
@@ -23395,7 +24033,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>184</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>994</v>
@@ -23466,7 +24104,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>185</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>856</v>
@@ -23537,7 +24175,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>186</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>965</v>
@@ -23608,7 +24246,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>187</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>949</v>
@@ -23679,7 +24317,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>393</v>
@@ -23750,7 +24388,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>9</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>460</v>
@@ -23821,7 +24459,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>983</v>
@@ -23892,7 +24530,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>46</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>528</v>
@@ -23963,7 +24601,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>10</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>774</v>
@@ -24034,7 +24672,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>610</v>
@@ -24105,7 +24743,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>12</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>1002</v>
@@ -24176,7 +24814,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>189</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>792</v>
@@ -24247,7 +24885,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>190</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>836</v>
@@ -24318,7 +24956,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>191</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>850</v>
@@ -24389,7 +25027,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>192</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>343</v>
@@ -24460,7 +25098,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>46</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>986</v>
@@ -24531,7 +25169,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>846</v>
@@ -24602,7 +25240,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>194</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>764</v>
@@ -24673,7 +25311,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>195</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>938</v>
@@ -24744,7 +25382,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>39</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>667</v>
@@ -24815,7 +25453,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>39</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>688</v>
@@ -24886,7 +25524,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>109</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>683</v>
@@ -24957,7 +25595,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>161</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>1093</v>
@@ -25028,7 +25666,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>46</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>895</v>
@@ -25099,7 +25737,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>196</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>396</v>
@@ -25170,7 +25808,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>197</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>1059</v>
@@ -25241,7 +25879,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>154</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>974</v>
@@ -25312,7 +25950,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>155</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>1005</v>
@@ -25383,7 +26021,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>39</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>893</v>
@@ -25454,7 +26092,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>198</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>1157</v>
@@ -25525,7 +26163,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>199</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>1194</v>
@@ -25596,7 +26234,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>200</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>1140</v>
@@ -25667,7 +26305,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>201</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>962</v>
@@ -25738,7 +26376,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>202</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>971</v>
@@ -25809,7 +26447,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>203</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>1197</v>
@@ -25880,7 +26518,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>204</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>1042</v>
@@ -25951,7 +26589,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>205</v>
+        <v>371</v>
       </c>
       <c r="C350">
         <v>1098</v>
@@ -26022,7 +26660,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>206</v>
+        <v>372</v>
       </c>
       <c r="C351">
         <v>985</v>
@@ -26093,7 +26731,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>207</v>
+        <v>373</v>
       </c>
       <c r="C352">
         <v>790</v>
@@ -26164,7 +26802,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>208</v>
+        <v>374</v>
       </c>
       <c r="C353">
         <v>686</v>
@@ -26235,7 +26873,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>209</v>
+        <v>375</v>
       </c>
       <c r="C354">
         <v>679</v>
@@ -26306,7 +26944,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>14</v>
+        <v>376</v>
       </c>
       <c r="C355">
         <v>1115</v>
@@ -26377,7 +27015,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>15</v>
+        <v>377</v>
       </c>
       <c r="C356">
         <v>1029</v>
@@ -26448,7 +27086,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>210</v>
+        <v>378</v>
       </c>
       <c r="C357">
         <v>1052</v>
@@ -26519,7 +27157,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>211</v>
+        <v>379</v>
       </c>
       <c r="C358">
         <v>1016</v>
@@ -26590,7 +27228,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>212</v>
+        <v>380</v>
       </c>
       <c r="C359">
         <v>603</v>
@@ -26661,7 +27299,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>154</v>
+        <v>381</v>
       </c>
       <c r="C360">
         <v>965</v>
@@ -26732,7 +27370,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>155</v>
+        <v>382</v>
       </c>
       <c r="C361">
         <v>773</v>
@@ -26803,7 +27441,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>213</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>701</v>
@@ -26874,7 +27512,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>214</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>716</v>
@@ -26945,7 +27583,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>215</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>667</v>
@@ -27016,7 +27654,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>216</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>671</v>
@@ -27087,7 +27725,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>217</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>1159</v>
@@ -27158,7 +27796,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>123</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>1206</v>
@@ -27229,7 +27867,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>9</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>204</v>
@@ -27300,7 +27938,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>31</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>863</v>
@@ -27371,7 +28009,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>30</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>127</v>
@@ -27442,7 +28080,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>46</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>381</v>
@@ -27513,7 +28151,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>218</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>342</v>
@@ -27584,7 +28222,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>352</v>
@@ -27655,7 +28293,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>125</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>607</v>
@@ -27726,7 +28364,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>219</v>
+        <v>396</v>
       </c>
       <c r="C375">
         <v>1156</v>
@@ -27797,7 +28435,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>220</v>
+        <v>397</v>
       </c>
       <c r="C376">
         <v>464</v>
@@ -27868,7 +28506,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>219</v>
+        <v>398</v>
       </c>
       <c r="C377">
         <v>743</v>
@@ -27939,7 +28577,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>221</v>
+        <v>399</v>
       </c>
       <c r="C378">
         <v>355</v>
@@ -28010,7 +28648,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>222</v>
+        <v>400</v>
       </c>
       <c r="C379">
         <v>827</v>
@@ -28081,7 +28719,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>223</v>
+        <v>401</v>
       </c>
       <c r="C380">
         <v>1191</v>
@@ -28152,7 +28790,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>224</v>
+        <v>402</v>
       </c>
       <c r="C381">
         <v>666</v>
@@ -28223,7 +28861,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>225</v>
+        <v>403</v>
       </c>
       <c r="C382">
         <v>684</v>
@@ -28294,7 +28932,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
       <c r="C383">
         <v>604</v>
@@ -28365,7 +29003,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>226</v>
+        <v>405</v>
       </c>
       <c r="C384">
         <v>849</v>
@@ -28436,7 +29074,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>227</v>
+        <v>406</v>
       </c>
       <c r="C385">
         <v>875</v>
@@ -28507,7 +29145,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>228</v>
+        <v>407</v>
       </c>
       <c r="C386">
         <v>1020</v>
@@ -28578,7 +29216,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>229</v>
+        <v>408</v>
       </c>
       <c r="C387">
         <v>846</v>
@@ -28649,7 +29287,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>230</v>
+        <v>409</v>
       </c>
       <c r="C388">
         <v>647</v>
@@ -28720,7 +29358,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>231</v>
+        <v>410</v>
       </c>
       <c r="C389">
         <v>441</v>
@@ -28791,7 +29429,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>47</v>
+        <v>411</v>
       </c>
       <c r="C390">
         <v>773</v>
@@ -28862,7 +29500,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>232</v>
+        <v>412</v>
       </c>
       <c r="C391">
         <v>597</v>
@@ -28933,7 +29571,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>233</v>
+        <v>413</v>
       </c>
       <c r="C392">
         <v>1141</v>
@@ -29004,7 +29642,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>234</v>
+        <v>414</v>
       </c>
       <c r="C393">
         <v>1053</v>
@@ -29075,7 +29713,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="C394">
         <v>1119</v>
@@ -29146,7 +29784,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>236</v>
+        <v>416</v>
       </c>
       <c r="C395">
         <v>855</v>
@@ -29217,7 +29855,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>237</v>
+        <v>417</v>
       </c>
       <c r="C396">
         <v>978</v>
@@ -29288,7 +29926,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>238</v>
+        <v>418</v>
       </c>
       <c r="C397">
         <v>1046</v>
@@ -29359,7 +29997,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>239</v>
+        <v>419</v>
       </c>
       <c r="C398">
         <v>905</v>
@@ -29430,7 +30068,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="C399">
         <v>1126</v>
@@ -29501,7 +30139,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>241</v>
+        <v>421</v>
       </c>
       <c r="C400">
         <v>926</v>
@@ -29572,7 +30210,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>242</v>
+        <v>422</v>
       </c>
       <c r="C401">
         <v>705</v>
@@ -29643,7 +30281,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>243</v>
+        <v>423</v>
       </c>
       <c r="C402">
         <v>1057</v>
@@ -29714,7 +30352,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>244</v>
+        <v>424</v>
       </c>
       <c r="C403">
         <v>1162</v>
@@ -29785,7 +30423,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>245</v>
+        <v>425</v>
       </c>
       <c r="C404">
         <v>901</v>
@@ -29856,7 +30494,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>246</v>
+        <v>426</v>
       </c>
       <c r="C405">
         <v>911</v>
@@ -29927,7 +30565,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>247</v>
+        <v>427</v>
       </c>
       <c r="C406">
         <v>1173</v>
@@ -29998,7 +30636,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="C407">
         <v>1165</v>
@@ -30069,7 +30707,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>249</v>
+        <v>429</v>
       </c>
       <c r="C408">
         <v>1100</v>
@@ -30140,7 +30778,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="C409">
         <v>813</v>
@@ -30211,7 +30849,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>249</v>
+        <v>431</v>
       </c>
       <c r="C410">
         <v>798</v>
@@ -30282,7 +30920,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>251</v>
+        <v>432</v>
       </c>
       <c r="C411">
         <v>1129</v>
@@ -30353,7 +30991,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>252</v>
+        <v>433</v>
       </c>
       <c r="C412">
         <v>652</v>
@@ -30424,7 +31062,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>253</v>
+        <v>434</v>
       </c>
       <c r="C413">
         <v>670</v>
@@ -30495,7 +31133,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>254</v>
+        <v>435</v>
       </c>
       <c r="C414">
         <v>987</v>
@@ -30566,7 +31204,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>255</v>
+        <v>436</v>
       </c>
       <c r="C415">
         <v>572</v>
@@ -30637,7 +31275,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>256</v>
+        <v>437</v>
       </c>
       <c r="C416">
         <v>410</v>
@@ -30708,7 +31346,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>257</v>
+        <v>438</v>
       </c>
       <c r="C417">
         <v>1005</v>
@@ -30779,7 +31417,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>258</v>
+        <v>439</v>
       </c>
       <c r="C418">
         <v>1078</v>
@@ -30850,7 +31488,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>259</v>
+        <v>440</v>
       </c>
       <c r="C419">
         <v>989</v>
@@ -30921,7 +31559,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>260</v>
+        <v>441</v>
       </c>
       <c r="C420">
         <v>733</v>
@@ -30992,7 +31630,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>261</v>
+        <v>442</v>
       </c>
       <c r="C421">
         <v>1215</v>
@@ -31063,7 +31701,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>262</v>
+        <v>443</v>
       </c>
       <c r="C422">
         <v>1112</v>
@@ -31134,7 +31772,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="C423">
         <v>685</v>
@@ -31205,7 +31843,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>264</v>
+        <v>445</v>
       </c>
       <c r="C424">
         <v>663</v>
@@ -31276,7 +31914,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>265</v>
+        <v>446</v>
       </c>
       <c r="C425">
         <v>1047</v>
@@ -31347,7 +31985,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>266</v>
+        <v>447</v>
       </c>
       <c r="C426">
         <v>1135</v>
@@ -31418,7 +32056,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>267</v>
+        <v>448</v>
       </c>
       <c r="C427">
         <v>1104</v>
@@ -31489,7 +32127,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>268</v>
+        <v>449</v>
       </c>
       <c r="C428">
         <v>1070</v>
@@ -31560,7 +32198,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>269</v>
+        <v>450</v>
       </c>
       <c r="C429">
         <v>832</v>
@@ -31631,7 +32269,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>270</v>
+        <v>451</v>
       </c>
       <c r="C430">
         <v>757</v>
@@ -31702,7 +32340,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>271</v>
+        <v>452</v>
       </c>
       <c r="C431">
         <v>692</v>
@@ -31773,7 +32411,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>272</v>
+        <v>453</v>
       </c>
       <c r="C432">
         <v>961</v>
@@ -31844,7 +32482,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>273</v>
+        <v>454</v>
       </c>
       <c r="C433">
         <v>756</v>
@@ -31915,7 +32553,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>273</v>
+        <v>455</v>
       </c>
       <c r="C434">
         <v>802</v>
